--- a/activity/M01A08/M01A08_PerfilValle.xlsx
+++ b/activity/M01A08/M01A08_PerfilValle.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/UECIJG.Student/HCMC2024.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1294" documentId="13_ncr:1_{2325EB46-7666-4D7C-9FFB-098ED79DB403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2B015CF-5A05-451F-A7F6-ED25ECEA3DF3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DA2325-E4DA-45B0-8850-69D54DBA55FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="7973" windowWidth="28996" windowHeight="16395" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>Observaciones</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Valor</t>
-  </si>
-  <si>
-    <t>Calificación: 1.8. Perfil de terreno del valle y evaluación de estructuras de caída para el canal a diseñar</t>
   </si>
   <si>
     <t>Perfil eje valle suavizado</t>
@@ -86,13 +83,7 @@
     <t>Alto escalones, m</t>
   </si>
   <si>
-    <t>Registrar los valores obtenidos en el libro de parámetros generales requeridos para el diseño y la modelación. Carpeta \HCMC0001\</t>
-  </si>
-  <si>
     <t>Opcional: verificación de formulación del libro suministrado para el diseño y análisis.</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Largo del eje del valle suavizado a partir de abscisas, m</t>
@@ -104,12 +95,6 @@
     <t>Análisis de perfil mayoritariamente en corte, relleno o ambos</t>
   </si>
   <si>
-    <t>https://pruebacorreoescuelaingeduco.sharepoint.com/sites/HCMC/SitePages/HCMC0008.aspx</t>
-  </si>
-  <si>
-    <t>Utilizando la plantilla Microsoft Word suministrada, cree un documento soporte mostrando las actividades desarrolladas junto con los análisis y recomendaciones realizados.</t>
-  </si>
-  <si>
     <t>Abscisa sección entrega modelo HEC-RAS valle , m</t>
   </si>
   <si>
@@ -119,16 +104,10 @@
     <t>Varios</t>
   </si>
   <si>
-    <t>Cargar en la carpeta \HCMC0008\ del repositorio de datos, el libro de cálculo HCMC0008_PerfilValle.xlsx con el resultado del análisis.</t>
-  </si>
-  <si>
     <t>Calificar sobre</t>
   </si>
   <si>
     <t>Calificación final</t>
-  </si>
-  <si>
-    <t>Largo valle reportado en entrega 1.7</t>
   </si>
   <si>
     <t>Calificación Instructor</t>
@@ -152,53 +131,52 @@
     <t>Grupo 5</t>
   </si>
   <si>
-    <t>Recomiendo ajustar la cota de fondo de la sección de inicio para que no sea necesario el uso de estructuras de caída para que las entregas laterales sean a fondo de valle.</t>
+    <t>Grupo 6</t>
   </si>
   <si>
-    <t>En el análisis falto explicar que para el tramo inicial a partir del km 8 es necesario realizar relleno en los extremos laterales del canal del valle para poder transportar el flujo de creciente para la sección adoptada de 3 metros de alto.</t>
+    <t>Grupo 7</t>
   </si>
   <si>
-    <t>En la entrega 1.7 definieron la cota de corona en 73.80 y en esta entrega están utilizando un valor de 73.70. (Justificado en informe)
-En el análisis falto explicar que para el tramo inicial a partir del km 8 es necesario realizar relleno en los extremos laterales del canal del valle para poder transportar el flujo de creciente para la sección adoptada de 3 metros de alto.</t>
+    <t>Grupo 8</t>
   </si>
   <si>
-    <t>Grafico auxiliar de cortes y rellenos no ajustado para que se visualice todo el valle</t>
+    <t>Grupo 9</t>
   </si>
   <si>
-    <t>El análisis realizado de localización de fondos en el inicio no es correcto, es necesario definir una cota de fondo ajustada considerando la profundidad de los sedimentos a remover en el proceso de construcción del nuevo alineamiento</t>
+    <t>Grupo 10</t>
   </si>
   <si>
-    <t>Localización incorrecta.</t>
+    <t>Grupo 11</t>
   </si>
   <si>
-    <t>Localización de fondos y coronas no es correcto, se debe buscar una cota de dragado en la sección de inicio que permita obtener un fondo de entrega de cauces laterales a la cota de fondo del nuevo valle. En la localización de estructuras han empalmado la corona del valle con el fondo del cauce lateral. En un canal de realineamiento no se pueden generar rampas negativas y zonas de depositación inversas.</t>
+    <t>Grupo 12</t>
   </si>
   <si>
-    <t>Grafico auxiliar de cortes y rellenos no ajustado para que se visualice todo el valle. Análisis presentados no son correctos.</t>
+    <t>Grupo 13</t>
   </si>
   <si>
-    <t>Grafico auxiliar de cortes y rellenos no ajustado para que se visualice todo el valle. Análisis presentados no son correctos. Informe sin gráficos de análisis de la hoja de diseño.</t>
+    <t>Grupo 14</t>
   </si>
   <si>
-    <t>No presentado. Se admite presentación extemporánea con calificación sobre 4.0.</t>
+    <t>Calificación: 1.8. Perfil de terreno del valle, evaluación de estructuras de caída y análisis de corte vs. relleno</t>
   </si>
   <si>
-    <t>Recomiendo volver a realizar el análisis del fondo del valle.</t>
+    <t>M01A08</t>
   </si>
   <si>
-    <t>Sección definida en 3 metros de alto.</t>
+    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A08/Readme.md</t>
   </si>
   <si>
-    <t>Gráficos no ajustados para visualizar el perfil completo y calculo de volúmenes a lo largo de todo el eje.</t>
+    <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
   </si>
   <si>
-    <t>El análisis realizado de localización de fondos en el inicio no es correcto, es necesario definir una cota de fondo ajustada considerando la profundidad de los sedimentos a remover en el proceso de construcción del nuevo alineamiento hasta un valor no mayor a 1 metro del fondo entregado. El fondo y corona utilizados en la sección de inicio no son correctos. En el gráfico no se observa el perfil completo</t>
+    <t>Registrar los valores obtenidos en el libro de parámetros generales requeridos para el diseño y la modelación.</t>
   </si>
   <si>
-    <t>Libro de parámetros siempre se almacena en carpeta HCMC0001. Análisis de cortes y rellenos incorrecto.</t>
+    <t>Largo valle reportado en entrega M01A07</t>
   </si>
   <si>
-    <t>Informe con poco detalle de los valores utilizados para los análisis, sin explicación de gráficos de análisis</t>
+    <t>Paralelas al valle curvo a una distancia de 150 metros</t>
   </si>
 </sst>
 </file>
@@ -206,10 +184,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0000000"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -260,12 +238,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="10"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
@@ -288,6 +260,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -303,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -473,19 +451,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -503,6 +468,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -510,9 +540,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -535,35 +565,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -590,7 +599,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -603,58 +612,83 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -715,7 +749,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>Calificación: 1.8. Perfil de terreno del valle y evaluación de estructuras de caída para el canal a diseñar</c:v>
+              <c:v>Calificación: 1.8. Perfil de terreno del valle, evaluación de estructuras de caída y análisis de corte vs. relleno</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -879,19 +913,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4.96875</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.96875</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.625</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1146,6 +1180,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1153,7 +1188,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1738,15 +1772,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>75541</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>18761</xdr:rowOff>
+      <xdr:colOff>108283</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>18760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>141540</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>51598</xdr:rowOff>
+      <xdr:colOff>138401</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>118486</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2074,322 +2108,323 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:F21"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.46484375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" style="20" customWidth="1"/>
-    <col min="3" max="4" width="10.53125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="20" customWidth="1"/>
-    <col min="8" max="16384" width="11.46484375" style="20"/>
+    <col min="1" max="1" width="2.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" style="14" customWidth="1"/>
+    <col min="3" max="4" width="10.53125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="10.53125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="11.46484375" style="14"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="F1" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>28</v>
+      <c r="C4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="21" t="s">
-        <v>32</v>
+      <c r="B5" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="C5" s="29">
         <v>5</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="11">
         <f>Detalle!C25*C5/5</f>
-        <v>4.9375</v>
-      </c>
-      <c r="E5" s="35">
-        <v>5</v>
-      </c>
-      <c r="F5" s="22">
+        <v>0</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="16">
         <f>AVERAGE(D5:E5)</f>
-        <v>4.96875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="21" t="s">
-        <v>33</v>
+      <c r="B6" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="29">
         <v>5</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="11">
         <f>Detalle!F25*C6/5</f>
-        <v>5</v>
-      </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="22">
+        <v>0</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="16">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="21" t="s">
-        <v>34</v>
+      <c r="B7" s="15" t="s">
+        <v>27</v>
       </c>
       <c r="C7" s="29">
         <v>5</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="11">
         <f>Detalle!I25*C7/5</f>
-        <v>4.96875</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="22">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="16">
         <f t="shared" si="0"/>
-        <v>4.96875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="21" t="s">
-        <v>35</v>
+      <c r="B8" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="C8" s="29">
         <v>5</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="11">
         <f>Detalle!L25*C8/5</f>
-        <v>3.25</v>
-      </c>
-      <c r="E8" s="35">
-        <v>5</v>
-      </c>
-      <c r="F8" s="22">
+        <v>0</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="16">
         <f t="shared" si="0"/>
-        <v>4.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="21" t="s">
-        <v>36</v>
+      <c r="B9" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="C9" s="29">
         <v>5</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="11">
         <f>Detalle!O25*C9/5</f>
-        <v>4.625</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="22">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="16">
         <f t="shared" si="0"/>
-        <v>4.625</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="21" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B10" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="C10" s="29">
         <v>5</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="11">
         <f>Detalle!R25*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="22">
+      <c r="E10" s="31"/>
+      <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="21" t="s">
-        <v>17</v>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B11" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="29">
         <v>5</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <f>Detalle!U25*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="22">
+      <c r="E11" s="31"/>
+      <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="21" t="s">
-        <v>17</v>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B12" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="C12" s="29">
         <v>5</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="11">
         <f>Detalle!X25*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="22">
+      <c r="E12" s="31"/>
+      <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="21" t="s">
-        <v>17</v>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="C13" s="29">
         <v>5</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="11">
         <f>Detalle!AA25*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="22">
+      <c r="E13" s="31"/>
+      <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="21" t="s">
-        <v>17</v>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="C14" s="29">
         <v>5</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="11">
         <f>Detalle!AD25*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="22">
+      <c r="E14" s="31"/>
+      <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="21" t="s">
-        <v>17</v>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B15" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="29">
         <v>5</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="11">
         <f>Detalle!AG25*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="22">
+      <c r="E15" s="31"/>
+      <c r="F15" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="21" t="s">
-        <v>17</v>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="29">
         <v>5</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="11">
         <f>Detalle!AJ25*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="22">
+      <c r="E16" s="31"/>
+      <c r="F16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="21" t="s">
-        <v>17</v>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="29">
         <v>5</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="11">
         <f>Detalle!AM25*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="22">
+      <c r="E17" s="31"/>
+      <c r="F17" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="23" t="s">
-        <v>17</v>
+      <c r="B18" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="C18" s="30">
         <v>5</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="23">
         <f>Detalle!AP25*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="37">
+      <c r="E18" s="32"/>
+      <c r="F18" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="B19" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B19:F20"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B19" r:id="rId1" xr:uid="{480EE820-7E5E-45A5-A213-BEC1ABD5A060}"/>
   </hyperlinks>
@@ -2439,1936 +2474,1407 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="A1" s="24"/>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="18"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="3" t="str">
+        <f>Calificacion!B2</f>
+        <v>Calificación: 1.8. Perfil de terreno del valle, evaluación de estructuras de caída y análisis de corte vs. relleno</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AM1" s="12"/>
+      <c r="AN1" s="12"/>
+      <c r="AP1" s="12"/>
+      <c r="AQ1" s="12"/>
     </row>
     <row r="2" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="48" t="str">
+      <c r="C2" s="49" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="48" t="str">
+      <c r="D2" s="50"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="49" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="48" t="str">
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="49" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="48" t="str">
+      <c r="J2" s="50"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="49" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="49"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="48" t="str">
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="49" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="48" t="str">
+      <c r="P2" s="50"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="49" t="str">
         <f>Calificacion!B10</f>
-        <v>N/A</v>
-      </c>
-      <c r="S2" s="49"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="48" t="str">
+        <v>Grupo 6</v>
+      </c>
+      <c r="S2" s="50"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="49" t="str">
         <f>Calificacion!B11</f>
-        <v>N/A</v>
-      </c>
-      <c r="V2" s="49"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="48" t="str">
+        <v>Grupo 7</v>
+      </c>
+      <c r="V2" s="50"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="49" t="str">
         <f>Calificacion!B12</f>
-        <v>N/A</v>
-      </c>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="48" t="str">
+        <v>Grupo 8</v>
+      </c>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="49" t="str">
         <f>Calificacion!B13</f>
-        <v>N/A</v>
-      </c>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="48" t="str">
+        <v>Grupo 9</v>
+      </c>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="49" t="str">
         <f>Calificacion!B14</f>
-        <v>N/A</v>
-      </c>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="48" t="str">
+        <v>Grupo 10</v>
+      </c>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="49" t="str">
         <f>Calificacion!B15</f>
-        <v>N/A</v>
-      </c>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="48" t="str">
+        <v>Grupo 11</v>
+      </c>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="49" t="str">
         <f>Calificacion!B16</f>
-        <v>N/A</v>
-      </c>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="50"/>
-      <c r="AM2" s="48" t="str">
+        <v>Grupo 12</v>
+      </c>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="49" t="str">
         <f>Calificacion!B17</f>
-        <v>N/A</v>
-      </c>
-      <c r="AN2" s="49"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="48" t="str">
+        <v>Grupo 13</v>
+      </c>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="49" t="str">
         <f>Calificacion!B18</f>
-        <v>N/A</v>
-      </c>
-      <c r="AQ2" s="49"/>
-      <c r="AR2" s="50"/>
+        <v>Grupo 14</v>
+      </c>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="51"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B3" s="47"/>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12" t="s">
+      <c r="H3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12" t="s">
+      <c r="K3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="12" t="s">
+      <c r="N3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="P3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="12" t="s">
+      <c r="Q3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="12" t="s">
+      <c r="T3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="V3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" s="12" t="s">
+      <c r="W3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="Y3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="12" t="s">
+      <c r="Z3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="12" t="s">
+      <c r="AC3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AE3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="12" t="s">
+      <c r="AF3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AH3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AI3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AI3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AK3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="12" t="s">
+      <c r="AL3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AN3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AO3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="12" t="s">
+      <c r="AO3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="AQ3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" s="15"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="15"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="16"/>
-      <c r="AD4" s="15"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="8"/>
-      <c r="AI4" s="16"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="8"/>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="15"/>
-      <c r="AN4" s="8"/>
-      <c r="AO4" s="16"/>
-      <c r="AP4" s="15"/>
-      <c r="AQ4" s="8"/>
-      <c r="AR4" s="16"/>
+      <c r="AR3" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B4" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="24"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="36"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="14">
+      <c r="B5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="35">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="35">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="35">
+        <v>0</v>
+      </c>
+      <c r="J5" s="24"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="35">
+        <v>0</v>
+      </c>
+      <c r="M5" s="24"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="35">
+        <v>0</v>
+      </c>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="35">
+        <v>0</v>
+      </c>
+      <c r="S5" s="24"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="35">
+        <v>0</v>
+      </c>
+      <c r="V5" s="24"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="35">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="36"/>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="35"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="35"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="35"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="24"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="24"/>
+      <c r="AR6" s="36"/>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="11">
+        <f>D5-D6</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="11">
+        <f>G5-G6</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="36"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="11">
+        <f>J5-J6</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="36"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="11">
+        <f>M5-M6</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="36"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="11">
+        <f>P5-P6</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="11">
+        <f>S5-S6</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="36"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="11">
+        <f>V5-V6</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="36"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="11">
+        <f>Y5-Y6</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="11">
+        <f>AB5-AB6</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="35"/>
+      <c r="AE7" s="11">
+        <f>AE5-AE6</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="11">
+        <f>AH5-AH6</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="35"/>
+      <c r="AK7" s="11">
+        <f>AK5-AK6</f>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="11">
+        <f>AN5-AN6</f>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="11">
+        <f>AQ5-AQ6</f>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="36"/>
+      <c r="AT7" s="11"/>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="35"/>
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="35"/>
+      <c r="AK8" s="24"/>
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="35"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="36"/>
+      <c r="AP8" s="35"/>
+      <c r="AQ8" s="24"/>
+      <c r="AR8" s="36"/>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="32">
-        <v>10827.6999740601</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="14">
-        <v>5</v>
-      </c>
-      <c r="G5" s="32">
-        <v>10753.6999969482</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="14">
-        <v>5</v>
-      </c>
-      <c r="J5" s="32">
-        <v>10826.2000274658</v>
-      </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="14">
-        <v>5</v>
-      </c>
-      <c r="M5" s="32">
-        <v>10826.600006103499</v>
-      </c>
-      <c r="N5" s="16"/>
-      <c r="O5" s="14">
-        <v>5</v>
-      </c>
-      <c r="P5" s="32">
-        <v>10826.3</v>
-      </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="14">
-        <v>0</v>
-      </c>
-      <c r="S5" s="32"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="14">
-        <v>0</v>
-      </c>
-      <c r="V5" s="32"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="16"/>
-      <c r="AD5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="16"/>
-      <c r="AJ5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="16"/>
-      <c r="AM5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="32"/>
-      <c r="AR5" s="16"/>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="14">
-        <v>5</v>
-      </c>
-      <c r="D6" s="32">
-        <v>3253.5</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="14">
-        <v>5</v>
-      </c>
-      <c r="G6" s="32">
-        <v>3253.5</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="14">
-        <v>5</v>
-      </c>
-      <c r="J6" s="32">
-        <v>3253.5</v>
-      </c>
-      <c r="K6" s="16"/>
-      <c r="L6" s="14">
-        <v>5</v>
-      </c>
-      <c r="M6" s="32">
-        <v>3246.1000061035202</v>
-      </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="14">
-        <v>5</v>
-      </c>
-      <c r="P6" s="32">
-        <v>3252.8</v>
-      </c>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="14">
-        <v>0</v>
-      </c>
-      <c r="S6" s="32"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="14">
-        <v>0</v>
-      </c>
-      <c r="V6" s="32"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="16"/>
-      <c r="AM6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="16"/>
-      <c r="AP6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="16"/>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="14">
-        <v>5</v>
-      </c>
-      <c r="D7" s="17">
-        <f>D5-D6</f>
-        <v>7574.1999740601004</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="14">
-        <v>5</v>
-      </c>
-      <c r="G7" s="17">
-        <f>G5-G6</f>
-        <v>7500.1999969482004</v>
-      </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="14">
-        <v>5</v>
-      </c>
-      <c r="J7" s="17">
-        <f>J5-J6</f>
-        <v>7572.7000274658003</v>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="14">
-        <v>5</v>
-      </c>
-      <c r="M7" s="17">
-        <f>M5-M6</f>
-        <v>7580.4999999999791</v>
-      </c>
-      <c r="N7" s="16"/>
-      <c r="O7" s="14">
-        <v>5</v>
-      </c>
-      <c r="P7" s="17">
-        <f>P5-P6</f>
-        <v>7573.4999999999991</v>
-      </c>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="14">
-        <v>0</v>
-      </c>
-      <c r="S7" s="17">
-        <f>S5-S6</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="16"/>
-      <c r="U7" s="14">
-        <v>0</v>
-      </c>
-      <c r="V7" s="17">
-        <f>V5-V6</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="16"/>
-      <c r="X7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="17">
-        <f>Y5-Y6</f>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="17">
-        <f>AB5-AB6</f>
-        <v>0</v>
-      </c>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="17">
-        <f>AE5-AE6</f>
-        <v>0</v>
-      </c>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="17">
-        <f>AH5-AH6</f>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="16"/>
-      <c r="AJ7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="17">
-        <f>AK5-AK6</f>
-        <v>0</v>
-      </c>
-      <c r="AL7" s="16"/>
-      <c r="AM7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="17">
-        <f>AN5-AN6</f>
-        <v>0</v>
-      </c>
-      <c r="AO7" s="16"/>
-      <c r="AP7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="17">
-        <f>AQ5-AQ6</f>
-        <v>0</v>
-      </c>
-      <c r="AR7" s="16"/>
-      <c r="AT7" s="17"/>
-    </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="14">
-        <v>5</v>
-      </c>
-      <c r="D8" s="32">
-        <v>7575</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="14">
-        <v>5</v>
-      </c>
-      <c r="G8" s="32">
-        <v>7569</v>
-      </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="14">
-        <v>5</v>
-      </c>
-      <c r="J8" s="32">
-        <v>7574.1</v>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="14">
-        <v>5</v>
-      </c>
-      <c r="M8" s="32">
-        <v>7580</v>
-      </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="14">
-        <v>5</v>
-      </c>
-      <c r="P8" s="17">
-        <v>7567</v>
-      </c>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="14">
-        <v>0</v>
-      </c>
-      <c r="S8" s="32"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="14">
-        <v>0</v>
-      </c>
-      <c r="V8" s="32"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="32"/>
-      <c r="AL8" s="16"/>
-      <c r="AM8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="16"/>
-      <c r="AP8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="32"/>
-      <c r="AR8" s="16"/>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="35"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="35"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="35"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="35"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="35"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="36"/>
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="14">
-        <v>5</v>
-      </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="14">
-        <v>5</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="14">
-        <v>5</v>
-      </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="14">
-        <v>5</v>
-      </c>
-      <c r="M9" s="32"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="14">
-        <v>5</v>
-      </c>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="14">
-        <v>0</v>
-      </c>
-      <c r="S9" s="32"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="14">
-        <v>0</v>
-      </c>
-      <c r="V9" s="32"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="32"/>
-      <c r="AO9" s="16"/>
-      <c r="AP9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="32"/>
-      <c r="AR9" s="16"/>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B10" s="10" t="s">
+      <c r="C10" s="35"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="36"/>
+      <c r="AM10" s="35"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="35"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="36"/>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="14">
-        <v>5</v>
-      </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="14">
-        <v>5</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="14">
-        <v>5</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="14">
-        <v>5</v>
-      </c>
-      <c r="M10" s="32"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="14">
-        <v>5</v>
-      </c>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="14">
-        <v>0</v>
-      </c>
-      <c r="S10" s="32"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="14">
-        <v>0</v>
-      </c>
-      <c r="V10" s="32"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="16"/>
-      <c r="AJ10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="16"/>
-      <c r="AM10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="16"/>
-      <c r="AP10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="32"/>
-      <c r="AR10" s="16"/>
-    </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="35"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="35"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="35"/>
+      <c r="AH11" s="24"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="35"/>
+      <c r="AK11" s="24"/>
+      <c r="AL11" s="36"/>
+      <c r="AM11" s="35"/>
+      <c r="AN11" s="24"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="35"/>
+      <c r="AQ11" s="24"/>
+      <c r="AR11" s="36"/>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="35"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="35"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="35"/>
+      <c r="AK12" s="24"/>
+      <c r="AL12" s="36"/>
+      <c r="AM12" s="35"/>
+      <c r="AN12" s="24"/>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="35"/>
+      <c r="AQ12" s="24"/>
+      <c r="AR12" s="36"/>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="35"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="35"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="35"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="24"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="35"/>
+      <c r="AN13" s="24"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="35"/>
+      <c r="AQ13" s="24"/>
+      <c r="AR13" s="36"/>
+    </row>
+    <row r="14" spans="1:46" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="14">
-        <v>5</v>
-      </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="14">
-        <v>5</v>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="14">
-        <v>5</v>
-      </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="14">
-        <v>5</v>
-      </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="14">
-        <v>5</v>
-      </c>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="14">
-        <v>0</v>
-      </c>
-      <c r="S11" s="32"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="14">
-        <v>0</v>
-      </c>
-      <c r="V11" s="32"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="32"/>
-      <c r="AL11" s="16"/>
-      <c r="AM11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="32"/>
-      <c r="AR11" s="16"/>
-    </row>
-    <row r="12" spans="1:46" ht="123" x14ac:dyDescent="0.45">
-      <c r="B12" s="10" t="s">
+      <c r="C14" s="35"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="35"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="35"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="35"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="36"/>
+      <c r="AM14" s="35"/>
+      <c r="AN14" s="24"/>
+      <c r="AO14" s="36"/>
+      <c r="AP14" s="35"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="36"/>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="35"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="36"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="28"/>
+      <c r="AO15" s="36"/>
+      <c r="AP15" s="35"/>
+      <c r="AQ15" s="28"/>
+      <c r="AR15" s="36"/>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="B16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="35"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="24"/>
+      <c r="AL16" s="36"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="24"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="24"/>
+      <c r="AR16" s="36"/>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="36"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="36"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17" s="24"/>
+      <c r="AI17" s="36"/>
+      <c r="AJ17" s="35"/>
+      <c r="AK17" s="24"/>
+      <c r="AL17" s="36"/>
+      <c r="AM17" s="35"/>
+      <c r="AN17" s="24"/>
+      <c r="AO17" s="36"/>
+      <c r="AP17" s="35"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="36"/>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="35"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="36"/>
+      <c r="AG18" s="35"/>
+      <c r="AH18" s="24"/>
+      <c r="AI18" s="36"/>
+      <c r="AJ18" s="35"/>
+      <c r="AK18" s="24"/>
+      <c r="AL18" s="36"/>
+      <c r="AM18" s="35"/>
+      <c r="AN18" s="24"/>
+      <c r="AO18" s="36"/>
+      <c r="AP18" s="35"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="36"/>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="24"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="35"/>
+      <c r="AK19" s="24"/>
+      <c r="AL19" s="36"/>
+      <c r="AM19" s="35"/>
+      <c r="AN19" s="24"/>
+      <c r="AO19" s="36"/>
+      <c r="AP19" s="35"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="36"/>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="14">
-        <v>5</v>
-      </c>
-      <c r="D12" s="32">
-        <v>1.55</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="14">
-        <v>5</v>
-      </c>
-      <c r="G12" s="32">
-        <v>1.43</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="14">
-        <v>5</v>
-      </c>
-      <c r="J12" s="32">
-        <v>2.35</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" s="15">
-        <v>1</v>
-      </c>
-      <c r="M12" s="32">
-        <v>0.93</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="15">
-        <v>1</v>
-      </c>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="R12" s="14">
-        <v>0</v>
-      </c>
-      <c r="S12" s="32"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="14">
-        <v>0</v>
-      </c>
-      <c r="V12" s="32"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="32"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="32"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="32"/>
-      <c r="AL12" s="16"/>
-      <c r="AM12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="32"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="32"/>
-      <c r="AR12" s="16"/>
-    </row>
-    <row r="13" spans="1:46" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B13" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="14"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="16"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="32"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="14"/>
-      <c r="AQ13" s="32"/>
-      <c r="AR13" s="16"/>
-    </row>
-    <row r="14" spans="1:46" ht="107.65" x14ac:dyDescent="0.45">
-      <c r="B14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="14">
-        <v>5</v>
-      </c>
-      <c r="D14" s="38">
-        <v>2.4599999999999999E-3</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="14">
-        <v>5</v>
-      </c>
-      <c r="G14" s="38">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="14">
-        <v>5</v>
-      </c>
-      <c r="J14" s="38">
-        <v>3.0200000000000001E-3</v>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="15">
-        <v>1</v>
-      </c>
-      <c r="M14" s="38">
-        <v>-6.2899999999999996E-3</v>
-      </c>
-      <c r="N14" s="16" t="s">
+      <c r="C20" s="35"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="24"/>
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="24"/>
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="35"/>
+      <c r="AK20" s="24"/>
+      <c r="AL20" s="36"/>
+      <c r="AM20" s="35"/>
+      <c r="AN20" s="24"/>
+      <c r="AO20" s="36"/>
+      <c r="AP20" s="35"/>
+      <c r="AQ20" s="24"/>
+      <c r="AR20" s="36"/>
+    </row>
+    <row r="21" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="36"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="36"/>
+      <c r="AJ21" s="35"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="36"/>
+      <c r="AM21" s="35"/>
+      <c r="AN21" s="25"/>
+      <c r="AO21" s="36"/>
+      <c r="AP21" s="35"/>
+      <c r="AQ21" s="25"/>
+      <c r="AR21" s="36"/>
+    </row>
+    <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B22" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="O14" s="14">
-        <v>5</v>
-      </c>
-      <c r="P14" s="38">
-        <v>5.5700000000000003E-3</v>
-      </c>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="14">
-        <v>0</v>
-      </c>
-      <c r="S14" s="38"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="14">
-        <v>0</v>
-      </c>
-      <c r="V14" s="38"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="38"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="38"/>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="38"/>
-      <c r="AI14" s="16"/>
-      <c r="AJ14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="38"/>
-      <c r="AL14" s="16"/>
-      <c r="AM14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="38"/>
-      <c r="AO14" s="16"/>
-      <c r="AP14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="38"/>
-      <c r="AR14" s="16"/>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="14">
-        <v>5</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="14">
-        <v>5</v>
-      </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="15">
-        <v>1</v>
-      </c>
-      <c r="M15" s="32"/>
-      <c r="N15" s="16" t="s">
+      <c r="C22" s="35"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="35"/>
+      <c r="AK22" s="24"/>
+      <c r="AL22" s="36"/>
+      <c r="AM22" s="35"/>
+      <c r="AN22" s="24"/>
+      <c r="AO22" s="36"/>
+      <c r="AP22" s="35"/>
+      <c r="AQ22" s="24"/>
+      <c r="AR22" s="36"/>
+    </row>
+    <row r="23" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
+      <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="O15" s="14">
-        <v>5</v>
-      </c>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="14">
-        <v>0</v>
-      </c>
-      <c r="S15" s="32"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="14">
-        <v>0</v>
-      </c>
-      <c r="V15" s="32"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="16"/>
-      <c r="AJ15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="32"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="32"/>
-      <c r="AO15" s="16"/>
-      <c r="AP15" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="32"/>
-      <c r="AR15" s="16"/>
-    </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="14">
-        <v>5</v>
-      </c>
-      <c r="G16" s="32">
-        <v>11</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="14">
-        <v>5</v>
-      </c>
-      <c r="J16" s="32">
-        <v>6</v>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="15">
-        <v>1</v>
-      </c>
-      <c r="M16" s="32">
-        <v>-5</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" s="14">
-        <v>5</v>
-      </c>
-      <c r="P16" s="32">
-        <v>5.6</v>
-      </c>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="14">
-        <v>0</v>
-      </c>
-      <c r="S16" s="32"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="14">
-        <v>0</v>
-      </c>
-      <c r="V16" s="32"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="16"/>
-      <c r="AG16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="16"/>
-      <c r="AJ16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="16"/>
-      <c r="AM16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="32"/>
-      <c r="AO16" s="16"/>
-      <c r="AP16" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="32"/>
-      <c r="AR16" s="16"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="14">
-        <v>5</v>
-      </c>
-      <c r="D17" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="14">
-        <v>5</v>
-      </c>
-      <c r="G17" s="32">
-        <v>0.1</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="14">
-        <v>5</v>
-      </c>
-      <c r="J17" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="15">
-        <v>1</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O17" s="14">
-        <v>5</v>
-      </c>
-      <c r="P17" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="14">
-        <v>0</v>
-      </c>
-      <c r="S17" s="32"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="14">
-        <v>0</v>
-      </c>
-      <c r="V17" s="32"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="16"/>
-      <c r="AM17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="32"/>
-      <c r="AO17" s="16"/>
-      <c r="AP17" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="32"/>
-      <c r="AR17" s="16"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="14">
-        <v>5</v>
-      </c>
-      <c r="D18" s="32">
-        <v>402.9</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="14">
-        <v>5</v>
-      </c>
-      <c r="G18" s="32">
-        <v>300</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="14">
-        <v>5</v>
-      </c>
-      <c r="J18" s="32">
-        <v>400.2</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="15">
-        <v>1</v>
-      </c>
-      <c r="M18" s="32">
-        <v>358.9</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O18" s="14">
-        <v>5</v>
-      </c>
-      <c r="P18" s="32">
-        <v>402.8</v>
-      </c>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="14">
-        <v>0</v>
-      </c>
-      <c r="S18" s="32"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="14">
-        <v>0</v>
-      </c>
-      <c r="V18" s="32"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="16"/>
-      <c r="AJ18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="16"/>
-      <c r="AM18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="32"/>
-      <c r="AO18" s="16"/>
-      <c r="AP18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="32"/>
-      <c r="AR18" s="16"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B19" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="9"/>
-      <c r="AG19" s="14"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="9"/>
-      <c r="AJ19" s="14"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="9"/>
-      <c r="AM19" s="14"/>
-      <c r="AN19" s="32"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="14"/>
-      <c r="AQ19" s="32"/>
-      <c r="AR19" s="9"/>
-    </row>
-    <row r="20" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
-      <c r="B20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="14">
-        <v>5</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="14">
-        <v>5</v>
-      </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="14">
-        <v>5</v>
-      </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L20" s="14">
-        <v>5</v>
-      </c>
-      <c r="M20" s="32"/>
-      <c r="N20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="O20" s="15">
-        <v>4.5</v>
-      </c>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="R20" s="14"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="9"/>
-      <c r="AG20" s="14"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="9"/>
-      <c r="AJ20" s="14"/>
-      <c r="AK20" s="32"/>
-      <c r="AL20" s="9"/>
-      <c r="AM20" s="14"/>
-      <c r="AN20" s="32"/>
-      <c r="AO20" s="9"/>
-      <c r="AP20" s="14"/>
-      <c r="AQ20" s="32"/>
-      <c r="AR20" s="9"/>
-    </row>
-    <row r="21" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
-      <c r="B21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="15">
-        <v>4.5</v>
-      </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="14">
-        <v>5</v>
-      </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="15">
-        <v>4.75</v>
-      </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21" s="15">
-        <v>3</v>
-      </c>
-      <c r="M21" s="32"/>
-      <c r="N21" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="O21" s="14">
-        <v>5</v>
-      </c>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="14">
-        <v>0</v>
-      </c>
-      <c r="S21" s="32"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="14">
-        <v>0</v>
-      </c>
-      <c r="V21" s="32"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="9"/>
-      <c r="AD21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="9"/>
-      <c r="AG21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="9"/>
-      <c r="AJ21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="9"/>
-      <c r="AM21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="32"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="32"/>
-      <c r="AR21" s="9"/>
-    </row>
-    <row r="22" spans="1:44" ht="49.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="15">
-        <v>4.5</v>
-      </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="14">
-        <v>5</v>
-      </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="15">
-        <v>4.75</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="15">
-        <v>3</v>
-      </c>
-      <c r="M22" s="32"/>
-      <c r="N22" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="O22" s="15">
-        <v>3.5</v>
-      </c>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="R22" s="14">
-        <v>0</v>
-      </c>
-      <c r="S22" s="32"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="14">
-        <v>0</v>
-      </c>
-      <c r="V22" s="32"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="16"/>
-      <c r="AG22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="16"/>
-      <c r="AJ22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="32"/>
-      <c r="AL22" s="16"/>
-      <c r="AM22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="32"/>
-      <c r="AO22" s="16"/>
-      <c r="AP22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="32"/>
-      <c r="AR22" s="16"/>
-    </row>
-    <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B23" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="9"/>
-      <c r="AG23" s="14"/>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="9"/>
-      <c r="AJ23" s="14"/>
-      <c r="AK23" s="33"/>
-      <c r="AL23" s="9"/>
-      <c r="AM23" s="14"/>
-      <c r="AN23" s="33"/>
-      <c r="AO23" s="9"/>
-      <c r="AP23" s="14"/>
-      <c r="AQ23" s="33"/>
-      <c r="AR23" s="9"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="36"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="36"/>
+      <c r="AG23" s="35"/>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="36"/>
+      <c r="AJ23" s="35"/>
+      <c r="AK23" s="24"/>
+      <c r="AL23" s="36"/>
+      <c r="AM23" s="35"/>
+      <c r="AN23" s="24"/>
+      <c r="AO23" s="36"/>
+      <c r="AP23" s="35"/>
+      <c r="AQ23" s="24"/>
+      <c r="AR23" s="36"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B24" s="10"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="9"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="9"/>
-      <c r="AG24" s="14"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="9"/>
-      <c r="AJ24" s="14"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="9"/>
-      <c r="AM24" s="14"/>
-      <c r="AN24" s="32"/>
-      <c r="AO24" s="9"/>
-      <c r="AP24" s="14"/>
-      <c r="AQ24" s="32"/>
-      <c r="AR24" s="9"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="38"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="38"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="38"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="40"/>
+      <c r="AJ24" s="38"/>
+      <c r="AK24" s="39"/>
+      <c r="AL24" s="40"/>
+      <c r="AM24" s="38"/>
+      <c r="AN24" s="39"/>
+      <c r="AO24" s="40"/>
+      <c r="AP24" s="38"/>
+      <c r="AQ24" s="39"/>
+      <c r="AR24" s="40"/>
     </row>
     <row r="25" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="45">
         <f>AVERAGE(C4:C24)</f>
-        <v>4.9375</v>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="43">
+        <v>0</v>
+      </c>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="45">
         <f>AVERAGE(F4:F24)</f>
-        <v>5</v>
-      </c>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="43">
+        <v>0</v>
+      </c>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="45">
         <f>AVERAGE(I4:I24)</f>
-        <v>4.96875</v>
-      </c>
-      <c r="J25" s="44"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="43">
+        <v>0</v>
+      </c>
+      <c r="J25" s="45"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="45">
         <f>AVERAGE(L4:L24)</f>
-        <v>3.25</v>
-      </c>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="43">
+        <v>0</v>
+      </c>
+      <c r="M25" s="45"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="45">
         <f>AVERAGE(O4:O24)</f>
-        <v>4.625</v>
-      </c>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="43">
+        <v>0</v>
+      </c>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="45">
         <f>AVERAGE(R4:R24)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="44"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="43">
+      <c r="S25" s="45"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="45">
         <f>AVERAGE(U4:U24)</f>
         <v>0</v>
       </c>
-      <c r="V25" s="44"/>
-      <c r="W25" s="45"/>
-      <c r="X25" s="43">
+      <c r="V25" s="45"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="45">
         <f>AVERAGE(X4:X24)</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="44"/>
-      <c r="Z25" s="45"/>
-      <c r="AA25" s="43">
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="45">
         <f>AVERAGE(AA4:AA24)</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="44"/>
-      <c r="AC25" s="45"/>
-      <c r="AD25" s="43">
+      <c r="AB25" s="45"/>
+      <c r="AC25" s="46"/>
+      <c r="AD25" s="45">
         <f>AVERAGE(AD4:AD24)</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="44"/>
-      <c r="AF25" s="45"/>
-      <c r="AG25" s="43">
+      <c r="AE25" s="45"/>
+      <c r="AF25" s="46"/>
+      <c r="AG25" s="45">
         <f>AVERAGE(AG4:AG24)</f>
         <v>0</v>
       </c>
-      <c r="AH25" s="44"/>
-      <c r="AI25" s="45"/>
-      <c r="AJ25" s="43">
+      <c r="AH25" s="45"/>
+      <c r="AI25" s="46"/>
+      <c r="AJ25" s="45">
         <f>AVERAGE(AJ4:AJ24)</f>
         <v>0</v>
       </c>
-      <c r="AK25" s="44"/>
-      <c r="AL25" s="45"/>
-      <c r="AM25" s="43">
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="46"/>
+      <c r="AM25" s="45">
         <f>AVERAGE(AM4:AM24)</f>
         <v>0</v>
       </c>
-      <c r="AN25" s="44"/>
-      <c r="AO25" s="45"/>
-      <c r="AP25" s="43">
+      <c r="AN25" s="45"/>
+      <c r="AO25" s="46"/>
+      <c r="AP25" s="45">
         <f>AVERAGE(AP4:AP24)</f>
         <v>0</v>
       </c>
-      <c r="AQ25" s="44"/>
-      <c r="AR25" s="45"/>
+      <c r="AQ25" s="45"/>
+      <c r="AR25" s="46"/>
     </row>
     <row r="26" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="19"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>

--- a/activity/M01A08/M01A08_PerfilValle.xlsx
+++ b/activity/M01A08/M01A08_PerfilValle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DA2325-E4DA-45B0-8850-69D54DBA55FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F4D4E3-B5D9-42F5-8E74-ADFFFE358219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
   <si>
     <t>Observaciones</t>
   </si>
@@ -164,9 +164,6 @@
     <t>M01A08</t>
   </si>
   <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A08/Readme.md</t>
-  </si>
-  <si>
     <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
   </si>
   <si>
@@ -250,12 +247,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -263,6 +254,12 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -281,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -460,15 +457,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -542,7 +530,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -645,11 +633,8 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -658,22 +643,22 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -681,21 +666,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -705,6 +675,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2126,20 +2111,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="22" t="s">
@@ -2397,20 +2382,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
+      <c r="B19" s="50" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A08 en GitHub.</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="26"/>
@@ -2420,17 +2406,15 @@
       <c r="F21" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{480EE820-7E5E-45A5-A213-BEC1ABD5A060}"/>
-  </hyperlinks>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2510,96 +2494,96 @@
     </row>
     <row r="2" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="49" t="str">
+      <c r="C2" s="43" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="49" t="str">
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="43" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="49" t="str">
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="43" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="49" t="str">
+      <c r="J2" s="44"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="43" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="50"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="49" t="str">
+      <c r="M2" s="44"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="43" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="49" t="str">
+      <c r="P2" s="44"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="43" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="49" t="str">
+      <c r="S2" s="44"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="43" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="50"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="49" t="str">
+      <c r="V2" s="44"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="43" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="49" t="str">
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="43" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="49" t="str">
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="43" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="49" t="str">
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="43" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="49" t="str">
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="43" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="49" t="str">
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="43" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="49" t="str">
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="43" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="51"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="45"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B3" s="48"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
@@ -2731,1147 +2715,1147 @@
       <c r="B4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="34"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="34"/>
       <c r="G4" s="24"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="34"/>
       <c r="J4" s="24"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="34"/>
       <c r="M4" s="24"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="34"/>
       <c r="P4" s="24"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="34"/>
       <c r="S4" s="24"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="34"/>
       <c r="V4" s="24"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="34"/>
       <c r="Y4" s="24"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="34"/>
       <c r="AB4" s="24"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="34"/>
       <c r="AE4" s="24"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="34"/>
       <c r="AH4" s="24"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="34"/>
       <c r="AK4" s="24"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="35"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="34"/>
       <c r="AN4" s="24"/>
-      <c r="AO4" s="36"/>
-      <c r="AP4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="34"/>
       <c r="AQ4" s="24"/>
-      <c r="AR4" s="36"/>
+      <c r="AR4" s="35"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="34">
         <v>0</v>
       </c>
       <c r="D5" s="24"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="35">
+      <c r="E5" s="35"/>
+      <c r="F5" s="34">
         <v>0</v>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="35">
+      <c r="H5" s="35"/>
+      <c r="I5" s="34">
         <v>0</v>
       </c>
       <c r="J5" s="24"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="35">
+      <c r="K5" s="35"/>
+      <c r="L5" s="34">
         <v>0</v>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="35">
+      <c r="N5" s="35"/>
+      <c r="O5" s="34">
         <v>0</v>
       </c>
       <c r="P5" s="24"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="35">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="34">
         <v>0</v>
       </c>
       <c r="S5" s="24"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="35">
+      <c r="T5" s="35"/>
+      <c r="U5" s="34">
         <v>0</v>
       </c>
       <c r="V5" s="24"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="35">
+      <c r="W5" s="35"/>
+      <c r="X5" s="34">
         <v>0</v>
       </c>
       <c r="Y5" s="24"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="35">
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="34">
         <v>0</v>
       </c>
       <c r="AB5" s="24"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="35">
+      <c r="AC5" s="35"/>
+      <c r="AD5" s="34">
         <v>0</v>
       </c>
       <c r="AE5" s="24"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="35">
+      <c r="AF5" s="35"/>
+      <c r="AG5" s="34">
         <v>0</v>
       </c>
       <c r="AH5" s="24"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="35">
+      <c r="AI5" s="35"/>
+      <c r="AJ5" s="34">
         <v>0</v>
       </c>
       <c r="AK5" s="24"/>
-      <c r="AL5" s="36"/>
-      <c r="AM5" s="35">
+      <c r="AL5" s="35"/>
+      <c r="AM5" s="34">
         <v>0</v>
       </c>
       <c r="AN5" s="24"/>
-      <c r="AO5" s="36"/>
-      <c r="AP5" s="35">
+      <c r="AO5" s="35"/>
+      <c r="AP5" s="34">
         <v>0</v>
       </c>
       <c r="AQ5" s="24"/>
-      <c r="AR5" s="36"/>
+      <c r="AR5" s="35"/>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="24"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="34"/>
       <c r="J6" s="24"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="34"/>
       <c r="P6" s="24"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="34"/>
       <c r="S6" s="24"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="34"/>
       <c r="V6" s="24"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="34"/>
       <c r="Y6" s="24"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="34"/>
       <c r="AB6" s="24"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="35"/>
+      <c r="AC6" s="35"/>
+      <c r="AD6" s="34"/>
       <c r="AE6" s="24"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="35"/>
+      <c r="AF6" s="35"/>
+      <c r="AG6" s="34"/>
       <c r="AH6" s="24"/>
-      <c r="AI6" s="36"/>
-      <c r="AJ6" s="35"/>
+      <c r="AI6" s="35"/>
+      <c r="AJ6" s="34"/>
       <c r="AK6" s="24"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="35"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="34"/>
       <c r="AN6" s="24"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="34"/>
       <c r="AQ6" s="24"/>
-      <c r="AR6" s="36"/>
+      <c r="AR6" s="35"/>
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="11">
         <f>D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="11">
         <f>G5-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="34"/>
       <c r="J7" s="11">
         <f>J5-J6</f>
         <v>0</v>
       </c>
-      <c r="K7" s="36"/>
-      <c r="L7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="11">
         <f>M5-M6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="36"/>
-      <c r="O7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="11">
         <f>P5-P6</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="34"/>
       <c r="S7" s="11">
         <f>S5-S6</f>
         <v>0</v>
       </c>
-      <c r="T7" s="36"/>
-      <c r="U7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="34"/>
       <c r="V7" s="11">
         <f>V5-V6</f>
         <v>0</v>
       </c>
-      <c r="W7" s="36"/>
-      <c r="X7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="34"/>
       <c r="Y7" s="11">
         <f>Y5-Y6</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="11">
         <f>AB5-AB6</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="35"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="34"/>
       <c r="AE7" s="11">
         <f>AE5-AE6</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="35"/>
+      <c r="AF7" s="35"/>
+      <c r="AG7" s="34"/>
       <c r="AH7" s="11">
         <f>AH5-AH6</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="35"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="34"/>
       <c r="AK7" s="11">
         <f>AK5-AK6</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="35"/>
+      <c r="AL7" s="35"/>
+      <c r="AM7" s="34"/>
       <c r="AN7" s="11">
         <f>AN5-AN6</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="34"/>
       <c r="AQ7" s="11">
         <f>AQ5-AQ6</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="36"/>
+      <c r="AR7" s="35"/>
       <c r="AT7" s="11"/>
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="35"/>
+        <v>43</v>
+      </c>
+      <c r="C8" s="34"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="34"/>
       <c r="J8" s="24"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="34"/>
       <c r="P8" s="24"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="34"/>
       <c r="S8" s="24"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="34"/>
       <c r="V8" s="24"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="34"/>
       <c r="Y8" s="24"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="34"/>
       <c r="AB8" s="24"/>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="35"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="34"/>
       <c r="AE8" s="24"/>
-      <c r="AF8" s="36"/>
-      <c r="AG8" s="35"/>
+      <c r="AF8" s="35"/>
+      <c r="AG8" s="34"/>
       <c r="AH8" s="24"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="35"/>
+      <c r="AI8" s="35"/>
+      <c r="AJ8" s="34"/>
       <c r="AK8" s="24"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="35"/>
+      <c r="AL8" s="35"/>
+      <c r="AM8" s="34"/>
       <c r="AN8" s="24"/>
-      <c r="AO8" s="36"/>
-      <c r="AP8" s="35"/>
+      <c r="AO8" s="35"/>
+      <c r="AP8" s="34"/>
       <c r="AQ8" s="24"/>
-      <c r="AR8" s="36"/>
+      <c r="AR8" s="35"/>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="24"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="24"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="34"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="24"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="34"/>
       <c r="P9" s="24"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="34"/>
       <c r="S9" s="24"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="34"/>
       <c r="V9" s="24"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="34"/>
       <c r="Y9" s="24"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="34"/>
       <c r="AB9" s="24"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AD9" s="34"/>
       <c r="AE9" s="24"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="35"/>
+      <c r="AF9" s="35"/>
+      <c r="AG9" s="34"/>
       <c r="AH9" s="24"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="35"/>
+      <c r="AI9" s="35"/>
+      <c r="AJ9" s="34"/>
       <c r="AK9" s="24"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="35"/>
+      <c r="AL9" s="35"/>
+      <c r="AM9" s="34"/>
       <c r="AN9" s="24"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="34"/>
       <c r="AQ9" s="24"/>
-      <c r="AR9" s="36"/>
+      <c r="AR9" s="35"/>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="24"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="24"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="34"/>
       <c r="P10" s="24"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="34"/>
       <c r="S10" s="24"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="34"/>
       <c r="V10" s="24"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="34"/>
       <c r="Y10" s="24"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="34"/>
       <c r="AB10" s="24"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="34"/>
       <c r="AE10" s="24"/>
-      <c r="AF10" s="36"/>
-      <c r="AG10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="34"/>
       <c r="AH10" s="24"/>
-      <c r="AI10" s="36"/>
-      <c r="AJ10" s="35"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="34"/>
       <c r="AK10" s="24"/>
-      <c r="AL10" s="36"/>
-      <c r="AM10" s="35"/>
+      <c r="AL10" s="35"/>
+      <c r="AM10" s="34"/>
       <c r="AN10" s="24"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AP10" s="34"/>
       <c r="AQ10" s="24"/>
-      <c r="AR10" s="36"/>
+      <c r="AR10" s="35"/>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="24"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="24"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="24"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="34"/>
       <c r="P11" s="24"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="34"/>
       <c r="S11" s="24"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="34"/>
       <c r="V11" s="24"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="34"/>
       <c r="Y11" s="24"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="34"/>
       <c r="AB11" s="24"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="35"/>
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="34"/>
       <c r="AE11" s="24"/>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="35"/>
+      <c r="AF11" s="35"/>
+      <c r="AG11" s="34"/>
       <c r="AH11" s="24"/>
-      <c r="AI11" s="36"/>
-      <c r="AJ11" s="35"/>
+      <c r="AI11" s="35"/>
+      <c r="AJ11" s="34"/>
       <c r="AK11" s="24"/>
-      <c r="AL11" s="36"/>
-      <c r="AM11" s="35"/>
+      <c r="AL11" s="35"/>
+      <c r="AM11" s="34"/>
       <c r="AN11" s="24"/>
-      <c r="AO11" s="36"/>
-      <c r="AP11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="34"/>
       <c r="AQ11" s="24"/>
-      <c r="AR11" s="36"/>
+      <c r="AR11" s="35"/>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="24"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="24"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="24"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="24"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="34"/>
       <c r="P12" s="24"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="34"/>
       <c r="S12" s="24"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="34"/>
       <c r="V12" s="24"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="34"/>
       <c r="Y12" s="24"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="34"/>
       <c r="AB12" s="24"/>
-      <c r="AC12" s="36"/>
-      <c r="AD12" s="35"/>
+      <c r="AC12" s="35"/>
+      <c r="AD12" s="34"/>
       <c r="AE12" s="24"/>
-      <c r="AF12" s="36"/>
-      <c r="AG12" s="35"/>
+      <c r="AF12" s="35"/>
+      <c r="AG12" s="34"/>
       <c r="AH12" s="24"/>
-      <c r="AI12" s="36"/>
-      <c r="AJ12" s="35"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="34"/>
       <c r="AK12" s="24"/>
-      <c r="AL12" s="36"/>
-      <c r="AM12" s="35"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="34"/>
       <c r="AN12" s="24"/>
-      <c r="AO12" s="36"/>
-      <c r="AP12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="34"/>
       <c r="AQ12" s="24"/>
-      <c r="AR12" s="36"/>
+      <c r="AR12" s="35"/>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="35"/>
+        <v>44</v>
+      </c>
+      <c r="C13" s="34"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="24"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="34"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="34"/>
       <c r="P13" s="24"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="34"/>
       <c r="S13" s="24"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="34"/>
       <c r="V13" s="24"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="34"/>
       <c r="Y13" s="24"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="34"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="36"/>
-      <c r="AD13" s="35"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="34"/>
       <c r="AE13" s="24"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="35"/>
+      <c r="AF13" s="35"/>
+      <c r="AG13" s="34"/>
       <c r="AH13" s="24"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="35"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="34"/>
       <c r="AK13" s="24"/>
-      <c r="AL13" s="36"/>
-      <c r="AM13" s="35"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="34"/>
       <c r="AN13" s="24"/>
-      <c r="AO13" s="36"/>
-      <c r="AP13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="34"/>
       <c r="AQ13" s="24"/>
-      <c r="AR13" s="36"/>
+      <c r="AR13" s="35"/>
     </row>
     <row r="14" spans="1:46" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="24"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="24"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="34"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="34"/>
       <c r="P14" s="24"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="34"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="34"/>
       <c r="V14" s="24"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="34"/>
       <c r="Y14" s="24"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="34"/>
       <c r="AB14" s="24"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="35"/>
+      <c r="AC14" s="35"/>
+      <c r="AD14" s="34"/>
       <c r="AE14" s="24"/>
-      <c r="AF14" s="36"/>
-      <c r="AG14" s="35"/>
+      <c r="AF14" s="35"/>
+      <c r="AG14" s="34"/>
       <c r="AH14" s="24"/>
-      <c r="AI14" s="36"/>
-      <c r="AJ14" s="35"/>
+      <c r="AI14" s="35"/>
+      <c r="AJ14" s="34"/>
       <c r="AK14" s="24"/>
-      <c r="AL14" s="36"/>
-      <c r="AM14" s="35"/>
+      <c r="AL14" s="35"/>
+      <c r="AM14" s="34"/>
       <c r="AN14" s="24"/>
-      <c r="AO14" s="36"/>
-      <c r="AP14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AP14" s="34"/>
       <c r="AQ14" s="24"/>
-      <c r="AR14" s="36"/>
+      <c r="AR14" s="35"/>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="28"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="28"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="34"/>
       <c r="J15" s="28"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="34"/>
       <c r="M15" s="28"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="34"/>
       <c r="P15" s="28"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="34"/>
       <c r="S15" s="28"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="34"/>
       <c r="V15" s="28"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="34"/>
       <c r="Y15" s="28"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="34"/>
       <c r="AB15" s="28"/>
-      <c r="AC15" s="36"/>
-      <c r="AD15" s="35"/>
+      <c r="AC15" s="35"/>
+      <c r="AD15" s="34"/>
       <c r="AE15" s="28"/>
-      <c r="AF15" s="36"/>
-      <c r="AG15" s="35"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="34"/>
       <c r="AH15" s="28"/>
-      <c r="AI15" s="36"/>
-      <c r="AJ15" s="35"/>
+      <c r="AI15" s="35"/>
+      <c r="AJ15" s="34"/>
       <c r="AK15" s="28"/>
-      <c r="AL15" s="36"/>
-      <c r="AM15" s="35"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="34"/>
       <c r="AN15" s="28"/>
-      <c r="AO15" s="36"/>
-      <c r="AP15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="34"/>
       <c r="AQ15" s="28"/>
-      <c r="AR15" s="36"/>
+      <c r="AR15" s="35"/>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="35"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="24"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="24"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="34"/>
       <c r="J16" s="24"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="34"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="34"/>
       <c r="P16" s="24"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="34"/>
       <c r="S16" s="24"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="34"/>
       <c r="V16" s="24"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="34"/>
       <c r="Y16" s="24"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="34"/>
       <c r="AB16" s="24"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="35"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="34"/>
       <c r="AE16" s="24"/>
-      <c r="AF16" s="36"/>
-      <c r="AG16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="34"/>
       <c r="AH16" s="24"/>
-      <c r="AI16" s="36"/>
-      <c r="AJ16" s="35"/>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="34"/>
       <c r="AK16" s="24"/>
-      <c r="AL16" s="36"/>
-      <c r="AM16" s="35"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="34"/>
       <c r="AN16" s="24"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="34"/>
       <c r="AQ16" s="24"/>
-      <c r="AR16" s="36"/>
+      <c r="AR16" s="35"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="35"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="24"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="34"/>
       <c r="J17" s="24"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="34"/>
       <c r="M17" s="24"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="34"/>
       <c r="P17" s="24"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="34"/>
       <c r="S17" s="24"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="34"/>
       <c r="V17" s="24"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="34"/>
       <c r="Y17" s="24"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="34"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="36"/>
-      <c r="AD17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="34"/>
       <c r="AE17" s="24"/>
-      <c r="AF17" s="36"/>
-      <c r="AG17" s="35"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="34"/>
       <c r="AH17" s="24"/>
-      <c r="AI17" s="36"/>
-      <c r="AJ17" s="35"/>
+      <c r="AI17" s="35"/>
+      <c r="AJ17" s="34"/>
       <c r="AK17" s="24"/>
-      <c r="AL17" s="36"/>
-      <c r="AM17" s="35"/>
+      <c r="AL17" s="35"/>
+      <c r="AM17" s="34"/>
       <c r="AN17" s="24"/>
-      <c r="AO17" s="36"/>
-      <c r="AP17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AP17" s="34"/>
       <c r="AQ17" s="24"/>
-      <c r="AR17" s="36"/>
+      <c r="AR17" s="35"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="24"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="24"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="34"/>
       <c r="M18" s="24"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="34"/>
       <c r="P18" s="24"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="34"/>
       <c r="S18" s="24"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="34"/>
       <c r="V18" s="24"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="34"/>
       <c r="Y18" s="24"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="34"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="36"/>
-      <c r="AD18" s="35"/>
+      <c r="AC18" s="35"/>
+      <c r="AD18" s="34"/>
       <c r="AE18" s="24"/>
-      <c r="AF18" s="36"/>
-      <c r="AG18" s="35"/>
+      <c r="AF18" s="35"/>
+      <c r="AG18" s="34"/>
       <c r="AH18" s="24"/>
-      <c r="AI18" s="36"/>
-      <c r="AJ18" s="35"/>
+      <c r="AI18" s="35"/>
+      <c r="AJ18" s="34"/>
       <c r="AK18" s="24"/>
-      <c r="AL18" s="36"/>
-      <c r="AM18" s="35"/>
+      <c r="AL18" s="35"/>
+      <c r="AM18" s="34"/>
       <c r="AN18" s="24"/>
-      <c r="AO18" s="36"/>
-      <c r="AP18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="34"/>
       <c r="AQ18" s="24"/>
-      <c r="AR18" s="36"/>
+      <c r="AR18" s="35"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="35"/>
+      <c r="C19" s="34"/>
       <c r="D19" s="24"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="34"/>
       <c r="J19" s="24"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="34"/>
       <c r="M19" s="24"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="34"/>
       <c r="P19" s="24"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="34"/>
       <c r="S19" s="24"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="34"/>
       <c r="V19" s="24"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="34"/>
       <c r="Y19" s="24"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="34"/>
       <c r="AB19" s="24"/>
-      <c r="AC19" s="36"/>
-      <c r="AD19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="34"/>
       <c r="AE19" s="24"/>
-      <c r="AF19" s="36"/>
-      <c r="AG19" s="35"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="34"/>
       <c r="AH19" s="24"/>
-      <c r="AI19" s="36"/>
-      <c r="AJ19" s="35"/>
+      <c r="AI19" s="35"/>
+      <c r="AJ19" s="34"/>
       <c r="AK19" s="24"/>
-      <c r="AL19" s="36"/>
-      <c r="AM19" s="35"/>
+      <c r="AL19" s="35"/>
+      <c r="AM19" s="34"/>
       <c r="AN19" s="24"/>
-      <c r="AO19" s="36"/>
-      <c r="AP19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="34"/>
       <c r="AQ19" s="24"/>
-      <c r="AR19" s="36"/>
+      <c r="AR19" s="35"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="35"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="24"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="24"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="34"/>
       <c r="J20" s="24"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="34"/>
       <c r="M20" s="24"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="34"/>
       <c r="P20" s="24"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="34"/>
       <c r="S20" s="24"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="34"/>
       <c r="V20" s="24"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="34"/>
       <c r="Y20" s="24"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="34"/>
       <c r="AB20" s="24"/>
-      <c r="AC20" s="36"/>
-      <c r="AD20" s="35"/>
+      <c r="AC20" s="35"/>
+      <c r="AD20" s="34"/>
       <c r="AE20" s="24"/>
-      <c r="AF20" s="36"/>
-      <c r="AG20" s="35"/>
+      <c r="AF20" s="35"/>
+      <c r="AG20" s="34"/>
       <c r="AH20" s="24"/>
-      <c r="AI20" s="36"/>
-      <c r="AJ20" s="35"/>
+      <c r="AI20" s="35"/>
+      <c r="AJ20" s="34"/>
       <c r="AK20" s="24"/>
-      <c r="AL20" s="36"/>
-      <c r="AM20" s="35"/>
+      <c r="AL20" s="35"/>
+      <c r="AM20" s="34"/>
       <c r="AN20" s="24"/>
-      <c r="AO20" s="36"/>
-      <c r="AP20" s="35"/>
+      <c r="AO20" s="35"/>
+      <c r="AP20" s="34"/>
       <c r="AQ20" s="24"/>
-      <c r="AR20" s="36"/>
+      <c r="AR20" s="35"/>
     </row>
     <row r="21" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="35"/>
+      <c r="C21" s="34"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="34"/>
       <c r="J21" s="25"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="34"/>
       <c r="M21" s="25"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="34"/>
       <c r="P21" s="25"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="34"/>
       <c r="S21" s="25"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="34"/>
       <c r="V21" s="25"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="34"/>
       <c r="Y21" s="25"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="34"/>
       <c r="AB21" s="25"/>
-      <c r="AC21" s="36"/>
-      <c r="AD21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="34"/>
       <c r="AE21" s="25"/>
-      <c r="AF21" s="36"/>
-      <c r="AG21" s="35"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="34"/>
       <c r="AH21" s="25"/>
-      <c r="AI21" s="36"/>
-      <c r="AJ21" s="35"/>
+      <c r="AI21" s="35"/>
+      <c r="AJ21" s="34"/>
       <c r="AK21" s="25"/>
-      <c r="AL21" s="36"/>
-      <c r="AM21" s="35"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="34"/>
       <c r="AN21" s="25"/>
-      <c r="AO21" s="36"/>
-      <c r="AP21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="34"/>
       <c r="AQ21" s="25"/>
-      <c r="AR21" s="36"/>
+      <c r="AR21" s="35"/>
     </row>
     <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B22" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="35"/>
+        <v>42</v>
+      </c>
+      <c r="C22" s="34"/>
       <c r="D22" s="24"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34"/>
       <c r="J22" s="24"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="34"/>
       <c r="M22" s="24"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="34"/>
       <c r="P22" s="24"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="34"/>
       <c r="S22" s="24"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="34"/>
       <c r="V22" s="24"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="34"/>
       <c r="Y22" s="24"/>
-      <c r="Z22" s="36"/>
-      <c r="AA22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="34"/>
       <c r="AB22" s="24"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="35"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="34"/>
       <c r="AE22" s="24"/>
-      <c r="AF22" s="36"/>
-      <c r="AG22" s="35"/>
+      <c r="AF22" s="35"/>
+      <c r="AG22" s="34"/>
       <c r="AH22" s="24"/>
-      <c r="AI22" s="36"/>
-      <c r="AJ22" s="35"/>
+      <c r="AI22" s="35"/>
+      <c r="AJ22" s="34"/>
       <c r="AK22" s="24"/>
-      <c r="AL22" s="36"/>
-      <c r="AM22" s="35"/>
+      <c r="AL22" s="35"/>
+      <c r="AM22" s="34"/>
       <c r="AN22" s="24"/>
-      <c r="AO22" s="36"/>
-      <c r="AP22" s="35"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="34"/>
       <c r="AQ22" s="24"/>
-      <c r="AR22" s="36"/>
+      <c r="AR22" s="35"/>
     </row>
     <row r="23" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B23" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="35"/>
+        <v>41</v>
+      </c>
+      <c r="C23" s="34"/>
       <c r="D23" s="24"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="24"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="34"/>
       <c r="J23" s="24"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="34"/>
       <c r="M23" s="24"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="34"/>
       <c r="P23" s="24"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="34"/>
       <c r="S23" s="24"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="34"/>
       <c r="V23" s="24"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="34"/>
       <c r="Y23" s="24"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="34"/>
       <c r="AB23" s="24"/>
-      <c r="AC23" s="36"/>
-      <c r="AD23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="34"/>
       <c r="AE23" s="24"/>
-      <c r="AF23" s="36"/>
-      <c r="AG23" s="35"/>
+      <c r="AF23" s="35"/>
+      <c r="AG23" s="34"/>
       <c r="AH23" s="24"/>
-      <c r="AI23" s="36"/>
-      <c r="AJ23" s="35"/>
+      <c r="AI23" s="35"/>
+      <c r="AJ23" s="34"/>
       <c r="AK23" s="24"/>
-      <c r="AL23" s="36"/>
-      <c r="AM23" s="35"/>
+      <c r="AL23" s="35"/>
+      <c r="AM23" s="34"/>
       <c r="AN23" s="24"/>
-      <c r="AO23" s="36"/>
-      <c r="AP23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="34"/>
       <c r="AQ23" s="24"/>
-      <c r="AR23" s="36"/>
+      <c r="AR23" s="35"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B24" s="37"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="38"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="38"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="40"/>
-      <c r="AA24" s="38"/>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="38"/>
-      <c r="AE24" s="39"/>
-      <c r="AF24" s="40"/>
-      <c r="AG24" s="38"/>
-      <c r="AH24" s="39"/>
-      <c r="AI24" s="40"/>
-      <c r="AJ24" s="38"/>
-      <c r="AK24" s="39"/>
-      <c r="AL24" s="40"/>
-      <c r="AM24" s="38"/>
-      <c r="AN24" s="39"/>
-      <c r="AO24" s="40"/>
-      <c r="AP24" s="38"/>
-      <c r="AQ24" s="39"/>
-      <c r="AR24" s="40"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="37"/>
+      <c r="Y24" s="38"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="38"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="37"/>
+      <c r="AE24" s="38"/>
+      <c r="AF24" s="39"/>
+      <c r="AG24" s="37"/>
+      <c r="AH24" s="38"/>
+      <c r="AI24" s="39"/>
+      <c r="AJ24" s="37"/>
+      <c r="AK24" s="38"/>
+      <c r="AL24" s="39"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="38"/>
+      <c r="AO24" s="39"/>
+      <c r="AP24" s="37"/>
+      <c r="AQ24" s="38"/>
+      <c r="AR24" s="39"/>
     </row>
     <row r="25" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="45">
+      <c r="C25" s="48">
         <f>AVERAGE(C4:C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="45">
+      <c r="D25" s="48"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="48">
         <f>AVERAGE(F4:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="45"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="45">
+      <c r="G25" s="48"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="48">
         <f>AVERAGE(I4:I24)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="45"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="45">
+      <c r="J25" s="48"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="48">
         <f>AVERAGE(L4:L24)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="45"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="45">
+      <c r="M25" s="48"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="48">
         <f>AVERAGE(O4:O24)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="45">
+      <c r="P25" s="48"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="48">
         <f>AVERAGE(R4:R24)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="45"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="45">
+      <c r="S25" s="48"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="48">
         <f>AVERAGE(U4:U24)</f>
         <v>0</v>
       </c>
-      <c r="V25" s="45"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="45">
+      <c r="V25" s="48"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="48">
         <f>AVERAGE(X4:X24)</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="45"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="45">
+      <c r="Y25" s="48"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="48">
         <f>AVERAGE(AA4:AA24)</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="45"/>
-      <c r="AC25" s="46"/>
-      <c r="AD25" s="45">
+      <c r="AB25" s="48"/>
+      <c r="AC25" s="49"/>
+      <c r="AD25" s="48">
         <f>AVERAGE(AD4:AD24)</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="45"/>
-      <c r="AF25" s="46"/>
-      <c r="AG25" s="45">
+      <c r="AE25" s="48"/>
+      <c r="AF25" s="49"/>
+      <c r="AG25" s="48">
         <f>AVERAGE(AG4:AG24)</f>
         <v>0</v>
       </c>
-      <c r="AH25" s="45"/>
-      <c r="AI25" s="46"/>
-      <c r="AJ25" s="45">
+      <c r="AH25" s="48"/>
+      <c r="AI25" s="49"/>
+      <c r="AJ25" s="48">
         <f>AVERAGE(AJ4:AJ24)</f>
         <v>0</v>
       </c>
-      <c r="AK25" s="45"/>
-      <c r="AL25" s="46"/>
-      <c r="AM25" s="45">
+      <c r="AK25" s="48"/>
+      <c r="AL25" s="49"/>
+      <c r="AM25" s="48">
         <f>AVERAGE(AM4:AM24)</f>
         <v>0</v>
       </c>
-      <c r="AN25" s="45"/>
-      <c r="AO25" s="46"/>
-      <c r="AP25" s="45">
+      <c r="AN25" s="48"/>
+      <c r="AO25" s="49"/>
+      <c r="AP25" s="48">
         <f>AVERAGE(AP4:AP24)</f>
         <v>0</v>
       </c>
-      <c r="AQ25" s="45"/>
-      <c r="AR25" s="46"/>
+      <c r="AQ25" s="48"/>
+      <c r="AR25" s="49"/>
     </row>
     <row r="26" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="13"/>
@@ -5495,11 +5479,14 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA25:AC25"/>
+    <mergeCell ref="AD25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="C2:E2"/>
@@ -5516,14 +5503,11 @@
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="R25:T25"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="AM25:AO25"/>
-    <mergeCell ref="X25:Z25"/>
-    <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="AD25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A08/M01A08_PerfilValle.xlsx
+++ b/activity/M01A08/M01A08_PerfilValle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F4D4E3-B5D9-42F5-8E74-ADFFFE358219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CB4B7D-531B-4D2C-91C3-FAA08EF0B9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -530,7 +530,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -621,12 +621,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -667,6 +661,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -687,9 +684,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -806,7 +800,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2106,25 +2102,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="22" t="s">
@@ -2154,7 +2150,7 @@
         <f>Detalle!C25*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="16">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2171,7 +2167,7 @@
         <f>Detalle!F25*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="16">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2188,7 +2184,7 @@
         <f>Detalle!I25*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2205,7 +2201,7 @@
         <f>Detalle!L25*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="31"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2222,7 +2218,7 @@
         <f>Detalle!O25*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="31"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,7 +2235,7 @@
         <f>Detalle!R25*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="31"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2256,7 +2252,7 @@
         <f>Detalle!U25*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="31"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2273,7 +2269,7 @@
         <f>Detalle!X25*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="31"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2290,7 +2286,7 @@
         <f>Detalle!AA25*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2307,7 +2303,7 @@
         <f>Detalle!AD25*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="31"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2324,7 +2320,7 @@
         <f>Detalle!AG25*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="31"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2341,7 +2337,7 @@
         <f>Detalle!AJ25*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="31"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2358,7 +2354,7 @@
         <f>Detalle!AM25*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="31"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2375,28 +2371,28 @@
         <f>Detalle!AP25*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="50" t="str">
+      <c r="B19" s="41" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A08 en GitHub.</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="26"/>
@@ -2494,96 +2490,96 @@
     </row>
     <row r="2" spans="1:46" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="43" t="str">
+      <c r="C2" s="42" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="43" t="str">
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="42" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="43" t="str">
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="42" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="43" t="str">
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="42" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="43" t="str">
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="42" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="43" t="str">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="42" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="44"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="43" t="str">
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="42" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="44"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="43" t="str">
+      <c r="V2" s="43"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="42" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="43" t="str">
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="42" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="43" t="str">
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="42" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="43" t="str">
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="42" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="43" t="str">
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="42" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="43" t="str">
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="42" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="43" t="str">
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="42" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="45"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="44"/>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.45">
-      <c r="B3" s="47"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
@@ -2715,1147 +2711,1147 @@
       <c r="B4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="34"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="34"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="32"/>
       <c r="G4" s="24"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="34"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="32"/>
       <c r="J4" s="24"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="34"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="32"/>
       <c r="M4" s="24"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="34"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="24"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="34"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="32"/>
       <c r="S4" s="24"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="34"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="32"/>
       <c r="V4" s="24"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="34"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="32"/>
       <c r="Y4" s="24"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="34"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="32"/>
       <c r="AB4" s="24"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="34"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="32"/>
       <c r="AE4" s="24"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="34"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="32"/>
       <c r="AH4" s="24"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="34"/>
+      <c r="AI4" s="33"/>
+      <c r="AJ4" s="32"/>
       <c r="AK4" s="24"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="34"/>
+      <c r="AL4" s="33"/>
+      <c r="AM4" s="32"/>
       <c r="AN4" s="24"/>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="34"/>
+      <c r="AO4" s="33"/>
+      <c r="AP4" s="32"/>
       <c r="AQ4" s="24"/>
-      <c r="AR4" s="35"/>
+      <c r="AR4" s="33"/>
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="32">
         <v>0</v>
       </c>
       <c r="D5" s="24"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="34">
+      <c r="E5" s="33"/>
+      <c r="F5" s="32">
         <v>0</v>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="34">
+      <c r="H5" s="33"/>
+      <c r="I5" s="32">
         <v>0</v>
       </c>
       <c r="J5" s="24"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="34">
+      <c r="K5" s="33"/>
+      <c r="L5" s="32">
         <v>0</v>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="34">
+      <c r="N5" s="33"/>
+      <c r="O5" s="32">
         <v>0</v>
       </c>
       <c r="P5" s="24"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="34">
+      <c r="Q5" s="33"/>
+      <c r="R5" s="32">
         <v>0</v>
       </c>
       <c r="S5" s="24"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="34">
+      <c r="T5" s="33"/>
+      <c r="U5" s="32">
         <v>0</v>
       </c>
       <c r="V5" s="24"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="34">
+      <c r="W5" s="33"/>
+      <c r="X5" s="32">
         <v>0</v>
       </c>
       <c r="Y5" s="24"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="34">
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="32">
         <v>0</v>
       </c>
       <c r="AB5" s="24"/>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="34">
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="32">
         <v>0</v>
       </c>
       <c r="AE5" s="24"/>
-      <c r="AF5" s="35"/>
-      <c r="AG5" s="34">
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="32">
         <v>0</v>
       </c>
       <c r="AH5" s="24"/>
-      <c r="AI5" s="35"/>
-      <c r="AJ5" s="34">
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="32">
         <v>0</v>
       </c>
       <c r="AK5" s="24"/>
-      <c r="AL5" s="35"/>
-      <c r="AM5" s="34">
+      <c r="AL5" s="33"/>
+      <c r="AM5" s="32">
         <v>0</v>
       </c>
       <c r="AN5" s="24"/>
-      <c r="AO5" s="35"/>
-      <c r="AP5" s="34">
+      <c r="AO5" s="33"/>
+      <c r="AP5" s="32">
         <v>0</v>
       </c>
       <c r="AQ5" s="24"/>
-      <c r="AR5" s="35"/>
+      <c r="AR5" s="33"/>
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="34"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="24"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="34"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="32"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="34"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="24"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="34"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="34"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="24"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="34"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="32"/>
       <c r="S6" s="24"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="34"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="32"/>
       <c r="V6" s="24"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="34"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="32"/>
       <c r="Y6" s="24"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="34"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="32"/>
       <c r="AB6" s="24"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="34"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="32"/>
       <c r="AE6" s="24"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6" s="34"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="32"/>
       <c r="AH6" s="24"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="34"/>
+      <c r="AI6" s="33"/>
+      <c r="AJ6" s="32"/>
       <c r="AK6" s="24"/>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="34"/>
+      <c r="AL6" s="33"/>
+      <c r="AM6" s="32"/>
       <c r="AN6" s="24"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="34"/>
+      <c r="AO6" s="33"/>
+      <c r="AP6" s="32"/>
       <c r="AQ6" s="24"/>
-      <c r="AR6" s="35"/>
+      <c r="AR6" s="33"/>
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="32"/>
       <c r="D7" s="11">
         <f>D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="34"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="32"/>
       <c r="G7" s="11">
         <f>G5-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="34"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="32"/>
       <c r="J7" s="11">
         <f>J5-J6</f>
         <v>0</v>
       </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="34"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="32"/>
       <c r="M7" s="11">
         <f>M5-M6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="34"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="11">
         <f>P5-P6</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="34"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="32"/>
       <c r="S7" s="11">
         <f>S5-S6</f>
         <v>0</v>
       </c>
-      <c r="T7" s="35"/>
-      <c r="U7" s="34"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="32"/>
       <c r="V7" s="11">
         <f>V5-V6</f>
         <v>0</v>
       </c>
-      <c r="W7" s="35"/>
-      <c r="X7" s="34"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="32"/>
       <c r="Y7" s="11">
         <f>Y5-Y6</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="34"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="32"/>
       <c r="AB7" s="11">
         <f>AB5-AB6</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="34"/>
+      <c r="AC7" s="33"/>
+      <c r="AD7" s="32"/>
       <c r="AE7" s="11">
         <f>AE5-AE6</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="35"/>
-      <c r="AG7" s="34"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="32"/>
       <c r="AH7" s="11">
         <f>AH5-AH6</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="35"/>
-      <c r="AJ7" s="34"/>
+      <c r="AI7" s="33"/>
+      <c r="AJ7" s="32"/>
       <c r="AK7" s="11">
         <f>AK5-AK6</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="35"/>
-      <c r="AM7" s="34"/>
+      <c r="AL7" s="33"/>
+      <c r="AM7" s="32"/>
       <c r="AN7" s="11">
         <f>AN5-AN6</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="34"/>
+      <c r="AO7" s="33"/>
+      <c r="AP7" s="32"/>
       <c r="AQ7" s="11">
         <f>AQ5-AQ6</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="35"/>
+      <c r="AR7" s="33"/>
       <c r="AT7" s="11"/>
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="34"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="34"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="34"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="24"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="34"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="34"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="24"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="34"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="32"/>
       <c r="S8" s="24"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="34"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="32"/>
       <c r="V8" s="24"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="34"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="32"/>
       <c r="Y8" s="24"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="34"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="32"/>
       <c r="AB8" s="24"/>
-      <c r="AC8" s="35"/>
-      <c r="AD8" s="34"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="32"/>
       <c r="AE8" s="24"/>
-      <c r="AF8" s="35"/>
-      <c r="AG8" s="34"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="32"/>
       <c r="AH8" s="24"/>
-      <c r="AI8" s="35"/>
-      <c r="AJ8" s="34"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="32"/>
       <c r="AK8" s="24"/>
-      <c r="AL8" s="35"/>
-      <c r="AM8" s="34"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="32"/>
       <c r="AN8" s="24"/>
-      <c r="AO8" s="35"/>
-      <c r="AP8" s="34"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="32"/>
       <c r="AQ8" s="24"/>
-      <c r="AR8" s="35"/>
+      <c r="AR8" s="33"/>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="34"/>
+      <c r="C9" s="32"/>
       <c r="D9" s="24"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="34"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="32"/>
       <c r="G9" s="24"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="34"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="32"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="34"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="32"/>
       <c r="M9" s="24"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="34"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="24"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="34"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="32"/>
       <c r="S9" s="24"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="34"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="32"/>
       <c r="V9" s="24"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="34"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="32"/>
       <c r="Y9" s="24"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="34"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="32"/>
       <c r="AB9" s="24"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="34"/>
+      <c r="AC9" s="33"/>
+      <c r="AD9" s="32"/>
       <c r="AE9" s="24"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="34"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="32"/>
       <c r="AH9" s="24"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="34"/>
+      <c r="AI9" s="33"/>
+      <c r="AJ9" s="32"/>
       <c r="AK9" s="24"/>
-      <c r="AL9" s="35"/>
-      <c r="AM9" s="34"/>
+      <c r="AL9" s="33"/>
+      <c r="AM9" s="32"/>
       <c r="AN9" s="24"/>
-      <c r="AO9" s="35"/>
-      <c r="AP9" s="34"/>
+      <c r="AO9" s="33"/>
+      <c r="AP9" s="32"/>
       <c r="AQ9" s="24"/>
-      <c r="AR9" s="35"/>
+      <c r="AR9" s="33"/>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="34"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="24"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="34"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="32"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="34"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="24"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="34"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="34"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="24"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="34"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="32"/>
       <c r="S10" s="24"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="34"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="32"/>
       <c r="V10" s="24"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="34"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="32"/>
       <c r="Y10" s="24"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="34"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="32"/>
       <c r="AB10" s="24"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="34"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="32"/>
       <c r="AE10" s="24"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="34"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="32"/>
       <c r="AH10" s="24"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="34"/>
+      <c r="AI10" s="33"/>
+      <c r="AJ10" s="32"/>
       <c r="AK10" s="24"/>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="34"/>
+      <c r="AL10" s="33"/>
+      <c r="AM10" s="32"/>
       <c r="AN10" s="24"/>
-      <c r="AO10" s="35"/>
-      <c r="AP10" s="34"/>
+      <c r="AO10" s="33"/>
+      <c r="AP10" s="32"/>
       <c r="AQ10" s="24"/>
-      <c r="AR10" s="35"/>
+      <c r="AR10" s="33"/>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="24"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="34"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="32"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="34"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="24"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="34"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="32"/>
       <c r="M11" s="24"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="34"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="24"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="34"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="32"/>
       <c r="S11" s="24"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="34"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="32"/>
       <c r="V11" s="24"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="34"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="32"/>
       <c r="Y11" s="24"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="34"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="32"/>
       <c r="AB11" s="24"/>
-      <c r="AC11" s="35"/>
-      <c r="AD11" s="34"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="32"/>
       <c r="AE11" s="24"/>
-      <c r="AF11" s="35"/>
-      <c r="AG11" s="34"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="32"/>
       <c r="AH11" s="24"/>
-      <c r="AI11" s="35"/>
-      <c r="AJ11" s="34"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="32"/>
       <c r="AK11" s="24"/>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="34"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="32"/>
       <c r="AN11" s="24"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="34"/>
+      <c r="AO11" s="33"/>
+      <c r="AP11" s="32"/>
       <c r="AQ11" s="24"/>
-      <c r="AR11" s="35"/>
+      <c r="AR11" s="33"/>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="24"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="34"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="32"/>
       <c r="G12" s="24"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="34"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="24"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="34"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="24"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="34"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="24"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="34"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="32"/>
       <c r="S12" s="24"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="34"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="32"/>
       <c r="V12" s="24"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="34"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="32"/>
       <c r="Y12" s="24"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="34"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="32"/>
       <c r="AB12" s="24"/>
-      <c r="AC12" s="35"/>
-      <c r="AD12" s="34"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="32"/>
       <c r="AE12" s="24"/>
-      <c r="AF12" s="35"/>
-      <c r="AG12" s="34"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="32"/>
       <c r="AH12" s="24"/>
-      <c r="AI12" s="35"/>
-      <c r="AJ12" s="34"/>
+      <c r="AI12" s="33"/>
+      <c r="AJ12" s="32"/>
       <c r="AK12" s="24"/>
-      <c r="AL12" s="35"/>
-      <c r="AM12" s="34"/>
+      <c r="AL12" s="33"/>
+      <c r="AM12" s="32"/>
       <c r="AN12" s="24"/>
-      <c r="AO12" s="35"/>
-      <c r="AP12" s="34"/>
+      <c r="AO12" s="33"/>
+      <c r="AP12" s="32"/>
       <c r="AQ12" s="24"/>
-      <c r="AR12" s="35"/>
+      <c r="AR12" s="33"/>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="34"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="32"/>
       <c r="G13" s="24"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="34"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="24"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="34"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="32"/>
       <c r="M13" s="24"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="34"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="24"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="34"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="32"/>
       <c r="S13" s="24"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="34"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="32"/>
       <c r="V13" s="24"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="34"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="32"/>
       <c r="Y13" s="24"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="34"/>
+      <c r="Z13" s="33"/>
+      <c r="AA13" s="32"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="34"/>
+      <c r="AC13" s="33"/>
+      <c r="AD13" s="32"/>
       <c r="AE13" s="24"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13" s="34"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="32"/>
       <c r="AH13" s="24"/>
-      <c r="AI13" s="35"/>
-      <c r="AJ13" s="34"/>
+      <c r="AI13" s="33"/>
+      <c r="AJ13" s="32"/>
       <c r="AK13" s="24"/>
-      <c r="AL13" s="35"/>
-      <c r="AM13" s="34"/>
+      <c r="AL13" s="33"/>
+      <c r="AM13" s="32"/>
       <c r="AN13" s="24"/>
-      <c r="AO13" s="35"/>
-      <c r="AP13" s="34"/>
+      <c r="AO13" s="33"/>
+      <c r="AP13" s="32"/>
       <c r="AQ13" s="24"/>
-      <c r="AR13" s="35"/>
+      <c r="AR13" s="33"/>
     </row>
     <row r="14" spans="1:46" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="24"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="34"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="34"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="24"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="34"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="32"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="34"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="24"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="34"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="32"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="34"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="32"/>
       <c r="V14" s="24"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="34"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="32"/>
       <c r="Y14" s="24"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="34"/>
+      <c r="Z14" s="33"/>
+      <c r="AA14" s="32"/>
       <c r="AB14" s="24"/>
-      <c r="AC14" s="35"/>
-      <c r="AD14" s="34"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="32"/>
       <c r="AE14" s="24"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="34"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="32"/>
       <c r="AH14" s="24"/>
-      <c r="AI14" s="35"/>
-      <c r="AJ14" s="34"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="32"/>
       <c r="AK14" s="24"/>
-      <c r="AL14" s="35"/>
-      <c r="AM14" s="34"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="32"/>
       <c r="AN14" s="24"/>
-      <c r="AO14" s="35"/>
-      <c r="AP14" s="34"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="32"/>
       <c r="AQ14" s="24"/>
-      <c r="AR14" s="35"/>
+      <c r="AR14" s="33"/>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="28"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="34"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="32"/>
       <c r="G15" s="28"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="34"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="32"/>
       <c r="J15" s="28"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="34"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="32"/>
       <c r="M15" s="28"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="34"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="28"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="34"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="32"/>
       <c r="S15" s="28"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="34"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="32"/>
       <c r="V15" s="28"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="34"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="32"/>
       <c r="Y15" s="28"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="34"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="32"/>
       <c r="AB15" s="28"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="34"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="32"/>
       <c r="AE15" s="28"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="34"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="32"/>
       <c r="AH15" s="28"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="34"/>
+      <c r="AI15" s="33"/>
+      <c r="AJ15" s="32"/>
       <c r="AK15" s="28"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="34"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="32"/>
       <c r="AN15" s="28"/>
-      <c r="AO15" s="35"/>
-      <c r="AP15" s="34"/>
+      <c r="AO15" s="33"/>
+      <c r="AP15" s="32"/>
       <c r="AQ15" s="28"/>
-      <c r="AR15" s="35"/>
+      <c r="AR15" s="33"/>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.45">
       <c r="B16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="34"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="24"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="34"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="32"/>
       <c r="G16" s="24"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="34"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="32"/>
       <c r="J16" s="24"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="34"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="32"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="34"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="24"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="34"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="32"/>
       <c r="S16" s="24"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="34"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="32"/>
       <c r="V16" s="24"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="34"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="32"/>
       <c r="Y16" s="24"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="34"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="32"/>
       <c r="AB16" s="24"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="34"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="32"/>
       <c r="AE16" s="24"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="34"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="32"/>
       <c r="AH16" s="24"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="34"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="32"/>
       <c r="AK16" s="24"/>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="34"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="32"/>
       <c r="AN16" s="24"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="34"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="32"/>
       <c r="AQ16" s="24"/>
-      <c r="AR16" s="35"/>
+      <c r="AR16" s="33"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="34"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="34"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="32"/>
       <c r="G17" s="24"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="34"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="32"/>
       <c r="J17" s="24"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="34"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="32"/>
       <c r="M17" s="24"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="34"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="24"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="34"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="32"/>
       <c r="S17" s="24"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="34"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="32"/>
       <c r="V17" s="24"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="34"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="32"/>
       <c r="Y17" s="24"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="34"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="32"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="35"/>
-      <c r="AD17" s="34"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="32"/>
       <c r="AE17" s="24"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17" s="34"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="32"/>
       <c r="AH17" s="24"/>
-      <c r="AI17" s="35"/>
-      <c r="AJ17" s="34"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="32"/>
       <c r="AK17" s="24"/>
-      <c r="AL17" s="35"/>
-      <c r="AM17" s="34"/>
+      <c r="AL17" s="33"/>
+      <c r="AM17" s="32"/>
       <c r="AN17" s="24"/>
-      <c r="AO17" s="35"/>
-      <c r="AP17" s="34"/>
+      <c r="AO17" s="33"/>
+      <c r="AP17" s="32"/>
       <c r="AQ17" s="24"/>
-      <c r="AR17" s="35"/>
+      <c r="AR17" s="33"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="34"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="24"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="34"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="32"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="34"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="24"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="34"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="32"/>
       <c r="M18" s="24"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="34"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="24"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="34"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="32"/>
       <c r="S18" s="24"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="34"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="32"/>
       <c r="V18" s="24"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="34"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="32"/>
       <c r="Y18" s="24"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="34"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="32"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="34"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="32"/>
       <c r="AE18" s="24"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="34"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="32"/>
       <c r="AH18" s="24"/>
-      <c r="AI18" s="35"/>
-      <c r="AJ18" s="34"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="32"/>
       <c r="AK18" s="24"/>
-      <c r="AL18" s="35"/>
-      <c r="AM18" s="34"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="32"/>
       <c r="AN18" s="24"/>
-      <c r="AO18" s="35"/>
-      <c r="AP18" s="34"/>
+      <c r="AO18" s="33"/>
+      <c r="AP18" s="32"/>
       <c r="AQ18" s="24"/>
-      <c r="AR18" s="35"/>
+      <c r="AR18" s="33"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="32"/>
       <c r="D19" s="24"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="34"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="32"/>
       <c r="G19" s="24"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="34"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="32"/>
       <c r="J19" s="24"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="34"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="32"/>
       <c r="M19" s="24"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="34"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="32"/>
       <c r="P19" s="24"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="34"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="32"/>
       <c r="S19" s="24"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="34"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="32"/>
       <c r="V19" s="24"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="34"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="32"/>
       <c r="Y19" s="24"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="34"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="32"/>
       <c r="AB19" s="24"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="34"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="32"/>
       <c r="AE19" s="24"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="34"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="32"/>
       <c r="AH19" s="24"/>
-      <c r="AI19" s="35"/>
-      <c r="AJ19" s="34"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="32"/>
       <c r="AK19" s="24"/>
-      <c r="AL19" s="35"/>
-      <c r="AM19" s="34"/>
+      <c r="AL19" s="33"/>
+      <c r="AM19" s="32"/>
       <c r="AN19" s="24"/>
-      <c r="AO19" s="35"/>
-      <c r="AP19" s="34"/>
+      <c r="AO19" s="33"/>
+      <c r="AP19" s="32"/>
       <c r="AQ19" s="24"/>
-      <c r="AR19" s="35"/>
+      <c r="AR19" s="33"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="32"/>
       <c r="D20" s="24"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="34"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="24"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="34"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="32"/>
       <c r="J20" s="24"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="34"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="32"/>
       <c r="M20" s="24"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="34"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="32"/>
       <c r="P20" s="24"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="34"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="32"/>
       <c r="S20" s="24"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="34"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="32"/>
       <c r="V20" s="24"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="34"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="32"/>
       <c r="Y20" s="24"/>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="34"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="32"/>
       <c r="AB20" s="24"/>
-      <c r="AC20" s="35"/>
-      <c r="AD20" s="34"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="32"/>
       <c r="AE20" s="24"/>
-      <c r="AF20" s="35"/>
-      <c r="AG20" s="34"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="32"/>
       <c r="AH20" s="24"/>
-      <c r="AI20" s="35"/>
-      <c r="AJ20" s="34"/>
+      <c r="AI20" s="33"/>
+      <c r="AJ20" s="32"/>
       <c r="AK20" s="24"/>
-      <c r="AL20" s="35"/>
-      <c r="AM20" s="34"/>
+      <c r="AL20" s="33"/>
+      <c r="AM20" s="32"/>
       <c r="AN20" s="24"/>
-      <c r="AO20" s="35"/>
-      <c r="AP20" s="34"/>
+      <c r="AO20" s="33"/>
+      <c r="AP20" s="32"/>
       <c r="AQ20" s="24"/>
-      <c r="AR20" s="35"/>
+      <c r="AR20" s="33"/>
     </row>
     <row r="21" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="34"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="25"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="34"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="32"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="34"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="32"/>
       <c r="J21" s="25"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="34"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="32"/>
       <c r="M21" s="25"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="34"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="32"/>
       <c r="P21" s="25"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="34"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="32"/>
       <c r="S21" s="25"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="34"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="32"/>
       <c r="V21" s="25"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="34"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="32"/>
       <c r="Y21" s="25"/>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="34"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="32"/>
       <c r="AB21" s="25"/>
-      <c r="AC21" s="35"/>
-      <c r="AD21" s="34"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="32"/>
       <c r="AE21" s="25"/>
-      <c r="AF21" s="35"/>
-      <c r="AG21" s="34"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="32"/>
       <c r="AH21" s="25"/>
-      <c r="AI21" s="35"/>
-      <c r="AJ21" s="34"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="32"/>
       <c r="AK21" s="25"/>
-      <c r="AL21" s="35"/>
-      <c r="AM21" s="34"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="32"/>
       <c r="AN21" s="25"/>
-      <c r="AO21" s="35"/>
-      <c r="AP21" s="34"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="32"/>
       <c r="AQ21" s="25"/>
-      <c r="AR21" s="35"/>
+      <c r="AR21" s="33"/>
     </row>
     <row r="22" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="34"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="24"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="34"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="32"/>
       <c r="G22" s="24"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="34"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="32"/>
       <c r="J22" s="24"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="34"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="32"/>
       <c r="M22" s="24"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="34"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="32"/>
       <c r="P22" s="24"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="34"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="32"/>
       <c r="S22" s="24"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="34"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="32"/>
       <c r="V22" s="24"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="34"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="32"/>
       <c r="Y22" s="24"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="34"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="32"/>
       <c r="AB22" s="24"/>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="34"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="32"/>
       <c r="AE22" s="24"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="34"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="32"/>
       <c r="AH22" s="24"/>
-      <c r="AI22" s="35"/>
-      <c r="AJ22" s="34"/>
+      <c r="AI22" s="33"/>
+      <c r="AJ22" s="32"/>
       <c r="AK22" s="24"/>
-      <c r="AL22" s="35"/>
-      <c r="AM22" s="34"/>
+      <c r="AL22" s="33"/>
+      <c r="AM22" s="32"/>
       <c r="AN22" s="24"/>
-      <c r="AO22" s="35"/>
-      <c r="AP22" s="34"/>
+      <c r="AO22" s="33"/>
+      <c r="AP22" s="32"/>
       <c r="AQ22" s="24"/>
-      <c r="AR22" s="35"/>
+      <c r="AR22" s="33"/>
     </row>
     <row r="23" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="34"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="24"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="34"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="32"/>
       <c r="G23" s="24"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="34"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="32"/>
       <c r="J23" s="24"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="34"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="32"/>
       <c r="M23" s="24"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="34"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="32"/>
       <c r="P23" s="24"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="34"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="32"/>
       <c r="S23" s="24"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="34"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="32"/>
       <c r="V23" s="24"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="34"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="32"/>
       <c r="Y23" s="24"/>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="34"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="32"/>
       <c r="AB23" s="24"/>
-      <c r="AC23" s="35"/>
-      <c r="AD23" s="34"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="32"/>
       <c r="AE23" s="24"/>
-      <c r="AF23" s="35"/>
-      <c r="AG23" s="34"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="32"/>
       <c r="AH23" s="24"/>
-      <c r="AI23" s="35"/>
-      <c r="AJ23" s="34"/>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="32"/>
       <c r="AK23" s="24"/>
-      <c r="AL23" s="35"/>
-      <c r="AM23" s="34"/>
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="32"/>
       <c r="AN23" s="24"/>
-      <c r="AO23" s="35"/>
-      <c r="AP23" s="34"/>
+      <c r="AO23" s="33"/>
+      <c r="AP23" s="32"/>
       <c r="AQ23" s="24"/>
-      <c r="AR23" s="35"/>
+      <c r="AR23" s="33"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="38"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="37"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="37"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="38"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="38"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="37"/>
-      <c r="AE24" s="38"/>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="37"/>
-      <c r="AH24" s="38"/>
-      <c r="AI24" s="39"/>
-      <c r="AJ24" s="37"/>
-      <c r="AK24" s="38"/>
-      <c r="AL24" s="39"/>
-      <c r="AM24" s="37"/>
-      <c r="AN24" s="38"/>
-      <c r="AO24" s="39"/>
-      <c r="AP24" s="37"/>
-      <c r="AQ24" s="38"/>
-      <c r="AR24" s="39"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="37"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="35"/>
+      <c r="AE24" s="36"/>
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="35"/>
+      <c r="AH24" s="36"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="35"/>
+      <c r="AK24" s="36"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="35"/>
+      <c r="AN24" s="36"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="35"/>
+      <c r="AQ24" s="36"/>
+      <c r="AR24" s="37"/>
     </row>
     <row r="25" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="47">
         <f>AVERAGE(C4:C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="48"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="48">
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="47">
         <f>AVERAGE(F4:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="48">
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="47">
         <f>AVERAGE(I4:I24)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="48"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="48">
+      <c r="J25" s="47"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="47">
         <f>AVERAGE(L4:L24)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="48"/>
-      <c r="N25" s="49"/>
-      <c r="O25" s="48">
+      <c r="M25" s="47"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="47">
         <f>AVERAGE(O4:O24)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="48">
+      <c r="P25" s="47"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="47">
         <f>AVERAGE(R4:R24)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="48"/>
-      <c r="T25" s="49"/>
-      <c r="U25" s="48">
+      <c r="S25" s="47"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="47">
         <f>AVERAGE(U4:U24)</f>
         <v>0</v>
       </c>
-      <c r="V25" s="48"/>
-      <c r="W25" s="49"/>
-      <c r="X25" s="48">
+      <c r="V25" s="47"/>
+      <c r="W25" s="48"/>
+      <c r="X25" s="47">
         <f>AVERAGE(X4:X24)</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="48"/>
-      <c r="Z25" s="49"/>
-      <c r="AA25" s="48">
+      <c r="Y25" s="47"/>
+      <c r="Z25" s="48"/>
+      <c r="AA25" s="47">
         <f>AVERAGE(AA4:AA24)</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="48"/>
-      <c r="AC25" s="49"/>
-      <c r="AD25" s="48">
+      <c r="AB25" s="47"/>
+      <c r="AC25" s="48"/>
+      <c r="AD25" s="47">
         <f>AVERAGE(AD4:AD24)</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="48"/>
-      <c r="AF25" s="49"/>
-      <c r="AG25" s="48">
+      <c r="AE25" s="47"/>
+      <c r="AF25" s="48"/>
+      <c r="AG25" s="47">
         <f>AVERAGE(AG4:AG24)</f>
         <v>0</v>
       </c>
-      <c r="AH25" s="48"/>
-      <c r="AI25" s="49"/>
-      <c r="AJ25" s="48">
+      <c r="AH25" s="47"/>
+      <c r="AI25" s="48"/>
+      <c r="AJ25" s="47">
         <f>AVERAGE(AJ4:AJ24)</f>
         <v>0</v>
       </c>
-      <c r="AK25" s="48"/>
-      <c r="AL25" s="49"/>
-      <c r="AM25" s="48">
+      <c r="AK25" s="47"/>
+      <c r="AL25" s="48"/>
+      <c r="AM25" s="47">
         <f>AVERAGE(AM4:AM24)</f>
         <v>0</v>
       </c>
-      <c r="AN25" s="48"/>
-      <c r="AO25" s="49"/>
-      <c r="AP25" s="48">
+      <c r="AN25" s="47"/>
+      <c r="AO25" s="48"/>
+      <c r="AP25" s="47">
         <f>AVERAGE(AP4:AP24)</f>
         <v>0</v>
       </c>
-      <c r="AQ25" s="48"/>
-      <c r="AR25" s="49"/>
+      <c r="AQ25" s="47"/>
+      <c r="AR25" s="48"/>
     </row>
     <row r="26" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="13"/>
